--- a/AAII_Financials/Yearly/CBU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CBU_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
+        <v>5300</v>
       </c>
       <c r="E14" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F14" s="3">
-        <v>1300</v>
+        <v>11600</v>
       </c>
       <c r="G14" s="3">
         <v>4700</v>
@@ -1128,13 +1128,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>507200</v>
+        <v>502100</v>
       </c>
       <c r="E17" s="3">
-        <v>472400</v>
+        <v>471800</v>
       </c>
       <c r="F17" s="3">
-        <v>456700</v>
+        <v>446400</v>
       </c>
       <c r="G17" s="3">
         <v>404300</v>
@@ -1179,13 +1179,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>289400</v>
+        <v>294600</v>
       </c>
       <c r="E18" s="3">
-        <v>251200</v>
+        <v>251800</v>
       </c>
       <c r="F18" s="3">
-        <v>184000</v>
+        <v>194300</v>
       </c>
       <c r="G18" s="3">
         <v>260200</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>305800</v>
+        <v>310900</v>
       </c>
       <c r="E21" s="3">
-        <v>265600</v>
+        <v>266200</v>
       </c>
       <c r="F21" s="3">
-        <v>197800</v>
+        <v>208100</v>
       </c>
       <c r="G21" s="3">
         <v>275500</v>
